--- a/SupprPrescAnaPhar/ig/StructureDefinition-fr-on-admission-medication-composition.xlsx
+++ b/SupprPrescAnaPhar/ig/StructureDefinition-fr-on-admission-medication-composition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T07:06:59+00:00</t>
+    <t>2026-05-27T07:17:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SupprPrescAnaPhar/ig/StructureDefinition-fr-on-admission-medication-composition.xlsx
+++ b/SupprPrescAnaPhar/ig/StructureDefinition-fr-on-admission-medication-composition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T07:17:52+00:00</t>
+    <t>2026-05-27T09:20:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
